--- a/server/assets/monthly-financial-report-template.xlsx
+++ b/server/assets/monthly-financial-report-template.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度结算" sheetId="1" r:id="Re6520feb0fa34728"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="手工项目明细" sheetId="2" r:id="R4c6104f3ebd74408"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自动来源明细" sheetId="3" r:id="Raa647e6ac09a4d5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校验" sheetId="4" r:id="R6892232b43564264"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度结算" sheetId="1" r:id="R27fe2ac76c8f46a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="手工项目明细" sheetId="2" r:id="R0fae2b175bce46dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自动来源明细" sheetId="3" r:id="R7edbb627df7044a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校验" sheetId="4" r:id="R4ea9ba8aa2154f70"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,10 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="¥#,##0.00;[Red]-¥#,##0.00;-"/>
+    <x:numFmt numFmtId="201" formatCode="&quot;¥&quot;#,##0.00;[Red]-&quot;¥&quot;#,##0.00;&quot;–&quot;"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -46,8 +47,59 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FF20242A"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="12"/>
+      <x:color rgb="FF20242A"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="24"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="15"/>
+      <x:color rgb="FFEFFFFD"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FF20242A"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13"/>
+      <x:color rgb="FF20242A"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="12"/>
+      <x:color rgb="FF20242A"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FF20242A"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -64,8 +116,63 @@
         <x:fgColor rgb="FF374151"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF73B2AA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF7F5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF8AB695"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF0F7F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE59A89"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFDF1EE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6C86D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF9E8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF7CAECB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEFF6FA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="19">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -95,11 +202,235 @@
         <x:color rgb="FFD1D5DB"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF73B2AA"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF73B2AA"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF73B2AA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF73B2AA"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF73B2AA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF73B2AA"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF73B2AA"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF73B2AA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD4DDDF"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD4DDDF"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD4DDDF"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD4DDDF"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF8AB695"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF8AB695"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF8AB695"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF8AB695"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF8AB695"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF8AB695"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF8AB695"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF8AB695"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE59A89"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FFE59A89"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FFE59A89"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FFE59A89"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FFE59A89"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE59A89"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FFE59A89"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FFE59A89"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6C86D"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FFE6C86D"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FFE6C86D"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FFE6C86D"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FFE6C86D"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE6C86D"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FFE6C86D"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FFE6C86D"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF7CAECB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF7CAECB"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF7CAECB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF7CAECB"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF7CAECB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF7CAECB"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF7CAECB"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="FF7CAECB"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="24">
+  <x:cellXfs count="93">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -159,6 +490,213 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="11" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="12" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="12" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -362,644 +900,644 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="19" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="19" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="19" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="38" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+    <x:row r="1" ht="50" customHeight="1">
+      <x:c r="A1" s="33" t="str">
         <x:v>月度结算</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="33" t="str">
         <x:v>月度结算</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="33" t="str">
         <x:v>月度结算</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="33" t="str">
         <x:v>月度结算</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="33" t="str">
         <x:v>月度结算</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="33" t="str">
         <x:v>月度结算</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="33" t="str">
         <x:v>月度结算</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="H1" s="33" t="str">
         <x:v>月度结算</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="8" t="str">
+    <x:row r="2" ht="34" customHeight="1">
+      <x:c r="A2" s="35" t="str">
         <x:v>2026年08月</x:v>
       </x:c>
-      <x:c r="B2" s="8" t="str">
+      <x:c r="B2" s="35" t="str">
         <x:v>2026年08月</x:v>
       </x:c>
-      <x:c r="C2" s="8" t="str">
+      <x:c r="C2" s="35" t="str">
         <x:v>2026年08月</x:v>
       </x:c>
-      <x:c r="D2" s="8" t="str">
+      <x:c r="D2" s="35" t="str">
         <x:v>2026年08月</x:v>
       </x:c>
-      <x:c r="E2" s="8" t="str">
+      <x:c r="E2" s="35" t="str">
         <x:v>2026年08月</x:v>
       </x:c>
-      <x:c r="F2" s="8" t="str">
+      <x:c r="F2" s="35" t="str">
         <x:v>2026年08月</x:v>
       </x:c>
-      <x:c r="G2" s="8" t="str">
+      <x:c r="G2" s="35" t="str">
         <x:v>2026年08月</x:v>
       </x:c>
-      <x:c r="H2" s="8" t="str">
+      <x:c r="H2" s="35" t="str">
         <x:v>2026年08月</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="3"/>
-      <x:c r="B3" s="3"/>
-      <x:c r="C3" s="3"/>
-      <x:c r="D3" s="3"/>
-      <x:c r="E3" s="3"/>
-      <x:c r="F3" s="3"/>
-      <x:c r="G3" s="3"/>
-      <x:c r="H3" s="3"/>
-    </x:row>
-    <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="11" t="str">
+    <x:row r="3" ht="18" customHeight="1">
+      <x:c r="A3" s="36"/>
+      <x:c r="B3" s="36"/>
+      <x:c r="C3" s="36"/>
+      <x:c r="D3" s="36"/>
+      <x:c r="E3" s="36"/>
+      <x:c r="F3" s="36"/>
+      <x:c r="G3" s="36"/>
+      <x:c r="H3" s="36"/>
+    </x:row>
+    <x:row r="4" ht="34" customHeight="1">
+      <x:c r="A4" s="39" t="str">
         <x:v>上月度（7月）-结算</x:v>
       </x:c>
-      <x:c r="B4" s="11" t="str">
+      <x:c r="B4" s="40" t="str">
         <x:v>上月度（7月）-结算</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="str">
+      <x:c r="C4" s="40" t="str">
         <x:v>上月度（7月）-结算</x:v>
       </x:c>
-      <x:c r="D4" s="11" t="str">
+      <x:c r="D4" s="40" t="str">
         <x:v>上月度（7月）-结算</x:v>
       </x:c>
-      <x:c r="E4" s="11" t="str">
+      <x:c r="E4" s="40" t="str">
         <x:v>上月度（7月）-结算</x:v>
       </x:c>
-      <x:c r="F4" s="11" t="str">
+      <x:c r="F4" s="40" t="str">
         <x:v>上月度（7月）-结算</x:v>
       </x:c>
-      <x:c r="G4" s="11" t="str">
+      <x:c r="G4" s="40" t="str">
         <x:v>上月度（7月）-结算</x:v>
       </x:c>
-      <x:c r="H4" s="11" t="str">
+      <x:c r="H4" s="41" t="str">
         <x:v>上月度（7月）-结算</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="14" t="str">
+    <x:row r="5" ht="40" customHeight="1">
+      <x:c r="A5" s="43" t="str">
         <x:v>团队可支配</x:v>
       </x:c>
-      <x:c r="B5" s="14"/>
-      <x:c r="C5" s="15" t="n">
+      <x:c r="B5" s="43"/>
+      <x:c r="C5" s="47" t="n">
         <x:f>ROUND(A7+C7+G7+H7,2)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D5" s="14"/>
-      <x:c r="E5" s="14"/>
-      <x:c r="F5" s="14"/>
-      <x:c r="G5" s="14"/>
-      <x:c r="H5" s="14"/>
-    </x:row>
-    <x:row r="6" ht="24" customHeight="1">
-      <x:c r="A6" s="14" t="str">
+      <x:c r="D5" s="47"/>
+      <x:c r="E5" s="47"/>
+      <x:c r="F5" s="47"/>
+      <x:c r="G5" s="47"/>
+      <x:c r="H5" s="47"/>
+    </x:row>
+    <x:row r="6" ht="36" customHeight="1">
+      <x:c r="A6" s="43" t="str">
         <x:v>一般账户</x:v>
       </x:c>
-      <x:c r="B6" s="14"/>
-      <x:c r="C6" s="14" t="str">
+      <x:c r="B6" s="43"/>
+      <x:c r="C6" s="43" t="str">
         <x:v>商务账户</x:v>
       </x:c>
-      <x:c r="D6" s="14"/>
-      <x:c r="E6" s="14" t="str">
+      <x:c r="D6" s="43"/>
+      <x:c r="E6" s="43" t="str">
         <x:v>福利金账户</x:v>
       </x:c>
-      <x:c r="F6" s="14"/>
-      <x:c r="G6" s="14" t="str">
+      <x:c r="F6" s="43"/>
+      <x:c r="G6" s="43" t="str">
         <x:v>福利金账户一</x:v>
       </x:c>
-      <x:c r="H6" s="14" t="str">
+      <x:c r="H6" s="43" t="str">
         <x:v>福利金账户二</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="24" customHeight="1">
-      <x:c r="A7" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B7" s="12"/>
-      <x:c r="C7" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D7" s="12"/>
-      <x:c r="E7" s="13" t="n">
+    <x:row r="7" ht="40" customHeight="1">
+      <x:c r="A7" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B7" s="51"/>
+      <x:c r="C7" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="51"/>
+      <x:c r="E7" s="51" t="n">
         <x:f>ROUND(G7+H7,2)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F7" s="12"/>
-      <x:c r="G7" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H7" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="24" customHeight="1">
-      <x:c r="A8" s="3"/>
-      <x:c r="B8" s="3"/>
-      <x:c r="C8" s="3"/>
-      <x:c r="D8" s="3"/>
-      <x:c r="E8" s="3"/>
-      <x:c r="F8" s="3"/>
-      <x:c r="G8" s="3"/>
-      <x:c r="H8" s="3"/>
-    </x:row>
-    <x:row r="9" ht="28" customHeight="1">
-      <x:c r="A9" s="11" t="str">
+      <x:c r="F7" s="51"/>
+      <x:c r="G7" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="16" customHeight="1">
+      <x:c r="A8" s="25"/>
+      <x:c r="B8" s="25"/>
+      <x:c r="C8" s="25"/>
+      <x:c r="D8" s="25"/>
+      <x:c r="E8" s="25"/>
+      <x:c r="F8" s="25"/>
+      <x:c r="G8" s="25"/>
+      <x:c r="H8" s="25"/>
+    </x:row>
+    <x:row r="9" ht="34" customHeight="1">
+      <x:c r="A9" s="54" t="str">
         <x:v>8月-收入汇总</x:v>
       </x:c>
-      <x:c r="B9" s="11" t="str">
+      <x:c r="B9" s="55" t="str">
         <x:v>8月-收入汇总</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="str">
+      <x:c r="C9" s="55" t="str">
         <x:v>8月-收入汇总</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="str">
+      <x:c r="D9" s="55" t="str">
         <x:v>8月-收入汇总</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="str">
+      <x:c r="E9" s="55" t="str">
         <x:v>8月-收入汇总</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="str">
+      <x:c r="F9" s="55" t="str">
         <x:v>8月-收入汇总</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="str">
+      <x:c r="G9" s="55" t="str">
         <x:v>8月-收入汇总</x:v>
       </x:c>
-      <x:c r="H9" s="11" t="str">
+      <x:c r="H9" s="56" t="str">
         <x:v>8月-收入汇总</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="24" customHeight="1">
-      <x:c r="A10" s="14" t="str">
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="58" t="str">
         <x:v>银行实际到账（入账合同额）</x:v>
       </x:c>
-      <x:c r="B10" s="14"/>
-      <x:c r="C10" s="14" t="str">
+      <x:c r="B10" s="58"/>
+      <x:c r="C10" s="58" t="str">
         <x:v>税费11.72%</x:v>
       </x:c>
-      <x:c r="D10" s="14" t="str">
+      <x:c r="D10" s="58" t="str">
         <x:v>营销5%</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="str">
+      <x:c r="E10" s="58" t="str">
         <x:v>商务10%</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="str">
+      <x:c r="F10" s="58" t="str">
         <x:v>核算基数</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="str">
+      <x:c r="G10" s="58" t="str">
         <x:v>一般账户利息</x:v>
       </x:c>
-      <x:c r="H10" s="14" t="str">
+      <x:c r="H10" s="58" t="str">
         <x:v>商务账户利息</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="24" customHeight="1">
-      <x:c r="A11" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B11" s="13"/>
-      <x:c r="C11" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E11" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F11" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="24" customHeight="1">
-      <x:c r="A12" s="3"/>
-      <x:c r="B12" s="3"/>
-      <x:c r="C12" s="3"/>
-      <x:c r="D12" s="3"/>
-      <x:c r="E12" s="3"/>
-      <x:c r="F12" s="3"/>
-      <x:c r="G12" s="3"/>
-      <x:c r="H12" s="3"/>
-    </x:row>
-    <x:row r="13" ht="28" customHeight="1">
-      <x:c r="A13" s="11" t="str">
+    <x:row r="11" ht="40" customHeight="1">
+      <x:c r="A11" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B11" s="60"/>
+      <x:c r="C11" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="16" customHeight="1">
+      <x:c r="A12" s="25"/>
+      <x:c r="B12" s="25"/>
+      <x:c r="C12" s="25"/>
+      <x:c r="D12" s="25"/>
+      <x:c r="E12" s="25"/>
+      <x:c r="F12" s="25"/>
+      <x:c r="G12" s="25"/>
+      <x:c r="H12" s="25"/>
+    </x:row>
+    <x:row r="13" ht="34" customHeight="1">
+      <x:c r="A13" s="63" t="str">
         <x:v>8月-支出汇总</x:v>
       </x:c>
-      <x:c r="B13" s="11" t="str">
+      <x:c r="B13" s="64" t="str">
         <x:v>8月-支出汇总</x:v>
       </x:c>
-      <x:c r="C13" s="11" t="str">
+      <x:c r="C13" s="64" t="str">
         <x:v>8月-支出汇总</x:v>
       </x:c>
-      <x:c r="D13" s="11" t="str">
+      <x:c r="D13" s="64" t="str">
         <x:v>8月-支出汇总</x:v>
       </x:c>
-      <x:c r="E13" s="11" t="str">
+      <x:c r="E13" s="64" t="str">
         <x:v>8月-支出汇总</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="str">
+      <x:c r="F13" s="64" t="str">
         <x:v>8月-支出汇总</x:v>
       </x:c>
-      <x:c r="G13" s="11" t="str">
+      <x:c r="G13" s="64" t="str">
         <x:v>8月-支出汇总</x:v>
       </x:c>
-      <x:c r="H13" s="11" t="str">
+      <x:c r="H13" s="65" t="str">
         <x:v>8月-支出汇总</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="34" customHeight="1">
-      <x:c r="A14" s="14" t="str">
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="68" t="str">
         <x:v>薪资+行政</x:v>
       </x:c>
-      <x:c r="B14" s="15" t="n">
+      <x:c r="B14" s="71" t="n">
         <x:f>ROUND(D15+E15+F15+A17,2)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C14" s="15"/>
-      <x:c r="D14" s="14" t="str">
+      <x:c r="C14" s="71"/>
+      <x:c r="D14" s="68" t="str">
         <x:v>薪资支出</x:v>
       </x:c>
-      <x:c r="E14" s="14" t="str">
+      <x:c r="E14" s="68" t="str">
         <x:v>其他支出</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="str">
+      <x:c r="F14" s="68" t="str">
         <x:v>一般账户跨行手续费</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="str">
+      <x:c r="G14" s="68" t="str">
         <x:v>商务账户跨行手续费</x:v>
       </x:c>
-      <x:c r="H14" s="14" t="str">
+      <x:c r="H14" s="68" t="str">
         <x:v>资产类合同支出总额</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="34" customHeight="1">
-      <x:c r="A15" s="12"/>
-      <x:c r="B15" s="13"/>
-      <x:c r="C15" s="13"/>
-      <x:c r="D15" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E15" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F15" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="24" customHeight="1">
-      <x:c r="A16" s="14" t="str">
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="68"/>
+      <x:c r="B15" s="71"/>
+      <x:c r="C15" s="71"/>
+      <x:c r="D15" s="72" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="72" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="72" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="72" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="72" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="36" customHeight="1">
+      <x:c r="A16" s="68" t="str">
         <x:v>行政汇总</x:v>
       </x:c>
-      <x:c r="B16" s="14" t="str">
+      <x:c r="B16" s="68" t="str">
         <x:v>人员1</x:v>
       </x:c>
-      <x:c r="C16" s="14" t="str">
+      <x:c r="C16" s="68" t="str">
         <x:v>人员2</x:v>
       </x:c>
-      <x:c r="D16" s="14" t="str">
+      <x:c r="D16" s="68" t="str">
         <x:v>人员3</x:v>
       </x:c>
-      <x:c r="E16" s="14" t="str">
+      <x:c r="E16" s="68" t="str">
         <x:v>人员4</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="str">
+      <x:c r="F16" s="68" t="str">
         <x:v>人员5</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="str">
+      <x:c r="G16" s="68" t="str">
         <x:v>人员6</x:v>
       </x:c>
-      <x:c r="H16" s="14" t="str">
+      <x:c r="H16" s="68" t="str">
         <x:v>其他人员</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="12" t="n">
+    <x:row r="17" ht="38" customHeight="1">
+      <x:c r="A17" s="51" t="n">
         <x:f>ROUND(SUM(B17:H17),2)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B17" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E17" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F17" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H17" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="24" customHeight="1">
-      <x:c r="A18" s="14" t="str">
+      <x:c r="B17" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C17" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="36" customHeight="1">
+      <x:c r="A18" s="68" t="str">
         <x:v>业务汇总</x:v>
       </x:c>
-      <x:c r="B18" s="14" t="str">
+      <x:c r="B18" s="68" t="str">
         <x:v>人员1</x:v>
       </x:c>
-      <x:c r="C18" s="14" t="str">
+      <x:c r="C18" s="68" t="str">
         <x:v>人员2</x:v>
       </x:c>
-      <x:c r="D18" s="14" t="str">
+      <x:c r="D18" s="68" t="str">
         <x:v>人员3</x:v>
       </x:c>
-      <x:c r="E18" s="14" t="str">
+      <x:c r="E18" s="68" t="str">
         <x:v>人员4</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="str">
+      <x:c r="F18" s="68" t="str">
         <x:v>人员5</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="str">
+      <x:c r="G18" s="68" t="str">
         <x:v>人员6</x:v>
       </x:c>
-      <x:c r="H18" s="14" t="str">
+      <x:c r="H18" s="68" t="str">
         <x:v>其他人员</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="24" customHeight="1">
-      <x:c r="A19" s="12" t="n">
+    <x:row r="19" ht="38" customHeight="1">
+      <x:c r="A19" s="51" t="n">
         <x:f>ROUND(SUM(B19:H19),2)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B19" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C19" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E19" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F19" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H19" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="24" customHeight="1">
-      <x:c r="A20" s="3"/>
-      <x:c r="B20" s="3"/>
-      <x:c r="C20" s="3"/>
-      <x:c r="D20" s="3"/>
-      <x:c r="E20" s="3"/>
-      <x:c r="F20" s="3"/>
-      <x:c r="G20" s="3"/>
-      <x:c r="H20" s="3"/>
-    </x:row>
-    <x:row r="21" ht="28" customHeight="1">
-      <x:c r="A21" s="11" t="str">
+      <x:c r="B19" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C19" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="16" customHeight="1">
+      <x:c r="A20" s="25"/>
+      <x:c r="B20" s="25"/>
+      <x:c r="C20" s="25"/>
+      <x:c r="D20" s="25"/>
+      <x:c r="E20" s="25"/>
+      <x:c r="F20" s="25"/>
+      <x:c r="G20" s="25"/>
+      <x:c r="H20" s="25"/>
+    </x:row>
+    <x:row r="21" ht="34" customHeight="1">
+      <x:c r="A21" s="75" t="str">
         <x:v>8月-福利金支出</x:v>
       </x:c>
-      <x:c r="B21" s="11" t="str">
+      <x:c r="B21" s="76" t="str">
         <x:v>8月-福利金支出</x:v>
       </x:c>
-      <x:c r="C21" s="11" t="str">
+      <x:c r="C21" s="76" t="str">
         <x:v>8月-福利金支出</x:v>
       </x:c>
-      <x:c r="D21" s="11" t="str">
+      <x:c r="D21" s="76" t="str">
         <x:v>8月-福利金支出</x:v>
       </x:c>
-      <x:c r="E21" s="11" t="str">
+      <x:c r="E21" s="76" t="str">
         <x:v>8月-福利金支出</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="str">
+      <x:c r="F21" s="76" t="str">
         <x:v>8月-福利金支出</x:v>
       </x:c>
-      <x:c r="G21" s="11" t="str">
+      <x:c r="G21" s="76" t="str">
         <x:v>8月-福利金支出</x:v>
       </x:c>
-      <x:c r="H21" s="11" t="str">
+      <x:c r="H21" s="77" t="str">
         <x:v>8月-福利金支出</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="24" customHeight="1">
-      <x:c r="A22" s="14" t="str">
+    <x:row r="22" ht="38" customHeight="1">
+      <x:c r="A22" s="81" t="str">
         <x:v>福利金汇总</x:v>
       </x:c>
-      <x:c r="B22" s="14" t="str">
+      <x:c r="B22" s="81" t="str">
         <x:v>账户一</x:v>
       </x:c>
-      <x:c r="C22" s="14" t="str">
+      <x:c r="C22" s="81" t="str">
         <x:v>饮用水</x:v>
       </x:c>
-      <x:c r="D22" s="14" t="str">
+      <x:c r="D22" s="81" t="str">
         <x:v>办公</x:v>
       </x:c>
-      <x:c r="E22" s="14" t="str">
+      <x:c r="E22" s="81" t="str">
         <x:v>电费</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="str">
+      <x:c r="F22" s="81" t="str">
         <x:v>407-AI</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="str">
+      <x:c r="G22" s="81" t="str">
         <x:v>8H-AI</x:v>
       </x:c>
-      <x:c r="H22" s="14" t="str"/>
-    </x:row>
-    <x:row r="23" ht="24" customHeight="1">
-      <x:c r="A23" s="13" t="n">
+      <x:c r="H22" s="81" t="str"/>
+    </x:row>
+    <x:row r="23" ht="38" customHeight="1">
+      <x:c r="A23" s="82"/>
+      <x:c r="B23" s="51" t="n">
+        <x:f>ROUND(SUM(C23:G23),2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C23" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E23" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F23" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G23" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H23" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="38" customHeight="1">
+      <x:c r="A24" s="71" t="n">
         <x:f>ROUND(B23+B25,2)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B23" s="13" t="n">
-        <x:f>ROUND(SUM(C23:G23),2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C23" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E23" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F23" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H23" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="24" customHeight="1">
-      <x:c r="A24" s="15" t="str"/>
-      <x:c r="B24" s="15" t="str">
+      <x:c r="B24" s="82" t="str">
         <x:v>账户二</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="str">
+      <x:c r="C24" s="82" t="str">
         <x:v>茶歇</x:v>
       </x:c>
-      <x:c r="D24" s="15" t="str">
+      <x:c r="D24" s="82" t="str">
         <x:v>团建</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="str">
+      <x:c r="E24" s="82" t="str">
         <x:v>体检</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="str"/>
-      <x:c r="G24" s="14" t="str"/>
-      <x:c r="H24" s="14" t="str"/>
-    </x:row>
-    <x:row r="25" ht="24" customHeight="1">
-      <x:c r="A25" s="13" t="str"/>
-      <x:c r="B25" s="13" t="n">
+      <x:c r="F24" s="82" t="str"/>
+      <x:c r="G24" s="81" t="str"/>
+      <x:c r="H24" s="81" t="str"/>
+    </x:row>
+    <x:row r="25" ht="38" customHeight="1">
+      <x:c r="A25" s="71"/>
+      <x:c r="B25" s="51" t="n">
         <x:f>ROUND(SUM(C25:E25),2)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C25" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D25" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E25" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F25" s="13" t="str"/>
-      <x:c r="G25" s="13" t="str"/>
-      <x:c r="H25" s="13" t="str"/>
-    </x:row>
-    <x:row r="26" ht="24" customHeight="1">
-      <x:c r="A26" s="3"/>
-      <x:c r="B26" s="3"/>
-      <x:c r="C26" s="3"/>
-      <x:c r="D26" s="3"/>
-      <x:c r="E26" s="3"/>
-      <x:c r="F26" s="3"/>
-      <x:c r="G26" s="3"/>
-      <x:c r="H26" s="3"/>
-    </x:row>
-    <x:row r="27" ht="28" customHeight="1">
-      <x:c r="A27" s="11" t="str">
+      <x:c r="C25" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D25" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E25" s="60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F25" s="60" t="str"/>
+      <x:c r="G25" s="60" t="str"/>
+      <x:c r="H25" s="60" t="str"/>
+    </x:row>
+    <x:row r="26" ht="16" customHeight="1">
+      <x:c r="A26" s="25"/>
+      <x:c r="B26" s="25"/>
+      <x:c r="C26" s="25"/>
+      <x:c r="D26" s="25"/>
+      <x:c r="E26" s="25"/>
+      <x:c r="F26" s="25"/>
+      <x:c r="G26" s="25"/>
+      <x:c r="H26" s="25"/>
+    </x:row>
+    <x:row r="27" ht="34" customHeight="1">
+      <x:c r="A27" s="85" t="str">
         <x:v>8月-结算</x:v>
       </x:c>
-      <x:c r="B27" s="11" t="str">
+      <x:c r="B27" s="86" t="str">
         <x:v>8月-结算</x:v>
       </x:c>
-      <x:c r="C27" s="11" t="str">
+      <x:c r="C27" s="86" t="str">
         <x:v>8月-结算</x:v>
       </x:c>
-      <x:c r="D27" s="11" t="str">
+      <x:c r="D27" s="86" t="str">
         <x:v>8月-结算</x:v>
       </x:c>
-      <x:c r="E27" s="11" t="str">
+      <x:c r="E27" s="86" t="str">
         <x:v>8月-结算</x:v>
       </x:c>
-      <x:c r="F27" s="11" t="str">
+      <x:c r="F27" s="86" t="str">
         <x:v>8月-结算</x:v>
       </x:c>
-      <x:c r="G27" s="11" t="str">
+      <x:c r="G27" s="86" t="str">
         <x:v>8月-结算</x:v>
       </x:c>
-      <x:c r="H27" s="11" t="str">
+      <x:c r="H27" s="87" t="str">
         <x:v>8月-结算</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="24" customHeight="1">
-      <x:c r="A28" s="14" t="str">
+    <x:row r="28" ht="42" customHeight="1">
+      <x:c r="A28" s="89" t="str">
         <x:v>团队可支配</x:v>
       </x:c>
-      <x:c r="B28" s="14"/>
-      <x:c r="C28" s="15" t="e">
-        <x:f>ROUND(B29+E29+G31+G32,2)</x:f>
-        <x:v>#VALUE!</x:v>
-      </x:c>
-      <x:c r="D28" s="14"/>
-      <x:c r="E28" s="14"/>
-      <x:c r="F28" s="14"/>
-      <x:c r="G28" s="14"/>
-      <x:c r="H28" s="14"/>
-    </x:row>
-    <x:row r="29" ht="30" customHeight="1">
-      <x:c r="A29" s="14" t="str">
+      <x:c r="B28" s="89"/>
+      <x:c r="C28" s="92" t="n">
+        <x:f>ROUND(B29+D29+F29,2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" s="92"/>
+      <x:c r="E28" s="92"/>
+      <x:c r="F28" s="92"/>
+      <x:c r="G28" s="92"/>
+      <x:c r="H28" s="92"/>
+    </x:row>
+    <x:row r="29" ht="42" customHeight="1">
+      <x:c r="A29" s="89" t="str">
         <x:v>一般-总额</x:v>
       </x:c>
-      <x:c r="B29" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C29" s="14" t="str">
+      <x:c r="B29" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="89" t="str">
         <x:v>商务-总额</x:v>
       </x:c>
-      <x:c r="D29" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E29" s="14" t="str">
-        <x:v>福利金-总额</x:v>
-      </x:c>
-      <x:c r="F29" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G29" s="14" t="str">
+      <x:c r="D29" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" s="89" t="str">
+        <x:v>福利金-商务-总额</x:v>
+      </x:c>
+      <x:c r="F29" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G29" s="89" t="str">
         <x:v>账户一-总额</x:v>
       </x:c>
-      <x:c r="H29" s="13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="30" customHeight="1">
-      <x:c r="A30" s="14" t="str"/>
-      <x:c r="B30" s="13" t="str"/>
-      <x:c r="C30" s="14" t="str"/>
-      <x:c r="D30" s="13" t="str"/>
-      <x:c r="E30" s="14" t="str"/>
-      <x:c r="F30" s="13" t="str"/>
-      <x:c r="G30" s="14" t="str">
+      <x:c r="H29" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="42" customHeight="1">
+      <x:c r="A30" s="89" t="str"/>
+      <x:c r="B30" s="51" t="str"/>
+      <x:c r="C30" s="89" t="str"/>
+      <x:c r="D30" s="51" t="str"/>
+      <x:c r="E30" s="89" t="str"/>
+      <x:c r="F30" s="51" t="str"/>
+      <x:c r="G30" s="89" t="str">
         <x:v>账户二-总额</x:v>
       </x:c>
-      <x:c r="H30" s="13" t="n">
+      <x:c r="H30" s="51" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1046,13 +1584,14 @@
     <x:mergeCell ref="A28:B28"/>
     <x:mergeCell ref="C28:H28"/>
     <x:mergeCell ref="B14:C15"/>
-    <x:mergeCell ref="A23:A25"/>
     <x:mergeCell ref="A29:A30"/>
     <x:mergeCell ref="B29:B30"/>
     <x:mergeCell ref="C29:C30"/>
     <x:mergeCell ref="D29:D30"/>
     <x:mergeCell ref="E29:E30"/>
     <x:mergeCell ref="F29:F30"/>
+    <x:mergeCell ref="A22:A23"/>
+    <x:mergeCell ref="A24:A25"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
